--- a/artfynd/A 23972-2026 artfynd.xlsx
+++ b/artfynd/A 23972-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849198</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134848964</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849039</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849252</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849274</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849307</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849343</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849411</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849532</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849987</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134850076</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134850184</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851216</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134852581</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849074</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851197</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134852043</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134852734</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849064</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849690</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849381</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2943,6 +3058,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849717</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3045,6 +3165,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134852433</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3147,6 +3272,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849729</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3249,6 +3379,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849723</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3351,6 +3486,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134848982</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3453,6 +3593,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849079</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3555,6 +3700,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134849617</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3657,6 +3807,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851224</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3763,6 +3918,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134850552</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3869,6 +4029,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134850657</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3975,6 +4140,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851333</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4081,6 +4251,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851379</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4187,6 +4362,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851594</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4293,6 +4473,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851814</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4399,6 +4584,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851894</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4505,6 +4695,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134851985</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4611,6 +4806,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134852088</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4717,6 +4917,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134852299</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4823,8 +5028,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134852833</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>